--- a/fixtures/demo-project/imports/06-test-packs.xlsx
+++ b/fixtures/demo-project/imports/06-test-packs.xlsx
@@ -501,8 +501,8 @@
       <c r="P2" t="str">
         <v>UPG-100-1001-S1</v>
       </c>
-      <c r="Q2">
-        <v>1</v>
+      <c r="Q2" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="3">
@@ -554,8 +554,8 @@
       <c r="P3" t="str">
         <v>UPG-100-1002-S1</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
+      <c r="Q3" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="4">
@@ -607,8 +607,8 @@
       <c r="P4" t="str">
         <v>UPG-100-1003-S1</v>
       </c>
-      <c r="Q4">
-        <v>1</v>
+      <c r="Q4" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="5">
@@ -660,8 +660,8 @@
       <c r="P5" t="str">
         <v>UPG-100-1004-S1</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
+      <c r="Q5" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="6">
@@ -713,8 +713,8 @@
       <c r="P6" t="str">
         <v>UPG-100-1005-S1</v>
       </c>
-      <c r="Q6">
-        <v>1</v>
+      <c r="Q6" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="7">
@@ -766,8 +766,8 @@
       <c r="P7" t="str">
         <v>UPG-100-1006-S1</v>
       </c>
-      <c r="Q7">
-        <v>1</v>
+      <c r="Q7" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="8">
@@ -819,8 +819,8 @@
       <c r="P8" t="str">
         <v>UPG-100-1007-S1</v>
       </c>
-      <c r="Q8">
-        <v>1</v>
+      <c r="Q8" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="9">
@@ -872,8 +872,8 @@
       <c r="P9" t="str">
         <v>UPG-100-1008-S1</v>
       </c>
-      <c r="Q9">
-        <v>1</v>
+      <c r="Q9" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="10">
@@ -925,8 +925,8 @@
       <c r="P10" t="str">
         <v>UPG-100-1009-S1</v>
       </c>
-      <c r="Q10">
-        <v>1</v>
+      <c r="Q10" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="11">
@@ -978,8 +978,8 @@
       <c r="P11" t="str">
         <v>UPG-100-1010-S1</v>
       </c>
-      <c r="Q11">
-        <v>1</v>
+      <c r="Q11" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="12">
@@ -1031,8 +1031,8 @@
       <c r="P12" t="str">
         <v>UPG-200-2001-S1</v>
       </c>
-      <c r="Q12">
-        <v>1</v>
+      <c r="Q12" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="13">
@@ -1084,8 +1084,8 @@
       <c r="P13" t="str">
         <v>UPG-200-2002-S1</v>
       </c>
-      <c r="Q13">
-        <v>1</v>
+      <c r="Q13" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="14">
@@ -1137,8 +1137,8 @@
       <c r="P14" t="str">
         <v>UPG-200-2003-S1</v>
       </c>
-      <c r="Q14">
-        <v>1</v>
+      <c r="Q14" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="15">
@@ -1190,8 +1190,8 @@
       <c r="P15" t="str">
         <v>UPG-200-2004-S1</v>
       </c>
-      <c r="Q15">
-        <v>1</v>
+      <c r="Q15" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="16">
@@ -1243,8 +1243,8 @@
       <c r="P16" t="str">
         <v>UPG-200-2005-S1</v>
       </c>
-      <c r="Q16">
-        <v>1</v>
+      <c r="Q16" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="17">
@@ -1296,8 +1296,8 @@
       <c r="P17" t="str">
         <v>UPG-200-2006-S1</v>
       </c>
-      <c r="Q17">
-        <v>1</v>
+      <c r="Q17" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="18">
@@ -1349,8 +1349,8 @@
       <c r="P18" t="str">
         <v>UPG-200-2007-S1</v>
       </c>
-      <c r="Q18">
-        <v>1</v>
+      <c r="Q18" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="19">
@@ -1402,8 +1402,8 @@
       <c r="P19" t="str">
         <v>UPG-200-2008-S1</v>
       </c>
-      <c r="Q19">
-        <v>1</v>
+      <c r="Q19" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="20">
@@ -1455,8 +1455,8 @@
       <c r="P20" t="str">
         <v>UPG-200-2009-S1</v>
       </c>
-      <c r="Q20">
-        <v>1</v>
+      <c r="Q20" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="21">
@@ -1508,8 +1508,8 @@
       <c r="P21" t="str">
         <v>UPG-200-2010-S1</v>
       </c>
-      <c r="Q21">
-        <v>1</v>
+      <c r="Q21" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="22">
@@ -1561,8 +1561,8 @@
       <c r="P22" t="str">
         <v>UPG-200-2011-S1</v>
       </c>
-      <c r="Q22">
-        <v>1</v>
+      <c r="Q22" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="23">
@@ -1614,8 +1614,8 @@
       <c r="P23" t="str">
         <v>UPG-200-2012-S1</v>
       </c>
-      <c r="Q23">
-        <v>1</v>
+      <c r="Q23" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="24">
@@ -1667,8 +1667,8 @@
       <c r="P24" t="str">
         <v>UPG-300-3001-S1</v>
       </c>
-      <c r="Q24">
-        <v>1</v>
+      <c r="Q24" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="25">
@@ -1720,8 +1720,8 @@
       <c r="P25" t="str">
         <v>UPG-300-3002-S1</v>
       </c>
-      <c r="Q25">
-        <v>1</v>
+      <c r="Q25" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="26">
@@ -1773,8 +1773,8 @@
       <c r="P26" t="str">
         <v>UPG-300-3003-S1</v>
       </c>
-      <c r="Q26">
-        <v>1</v>
+      <c r="Q26" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="27">
@@ -1826,8 +1826,8 @@
       <c r="P27" t="str">
         <v>UPG-300-3004-S1</v>
       </c>
-      <c r="Q27">
-        <v>1</v>
+      <c r="Q27" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="28">
@@ -1879,8 +1879,8 @@
       <c r="P28" t="str">
         <v>UPG-300-3005-S1</v>
       </c>
-      <c r="Q28">
-        <v>1</v>
+      <c r="Q28" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="29">
@@ -1932,8 +1932,8 @@
       <c r="P29" t="str">
         <v>UPG-300-3006-S1</v>
       </c>
-      <c r="Q29">
-        <v>1</v>
+      <c r="Q29" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="30">
@@ -1985,8 +1985,8 @@
       <c r="P30" t="str">
         <v>UPG-300-3007-S1</v>
       </c>
-      <c r="Q30">
-        <v>1</v>
+      <c r="Q30" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="31">
@@ -2038,8 +2038,8 @@
       <c r="P31" t="str">
         <v>UPG-300-3008-S1</v>
       </c>
-      <c r="Q31">
-        <v>1</v>
+      <c r="Q31" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="32">
@@ -2091,8 +2091,8 @@
       <c r="P32" t="str">
         <v>UPG-300-3009-S1</v>
       </c>
-      <c r="Q32">
-        <v>1</v>
+      <c r="Q32" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="33">
@@ -2144,8 +2144,8 @@
       <c r="P33" t="str">
         <v>UPG-300-3010-S1</v>
       </c>
-      <c r="Q33">
-        <v>1</v>
+      <c r="Q33" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="34">
@@ -2197,8 +2197,8 @@
       <c r="P34" t="str">
         <v>UPG-300-3011-S1</v>
       </c>
-      <c r="Q34">
-        <v>1</v>
+      <c r="Q34" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="35">
@@ -2250,8 +2250,8 @@
       <c r="P35" t="str">
         <v>UPG-300-3012-S1</v>
       </c>
-      <c r="Q35">
-        <v>1</v>
+      <c r="Q35" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="36">
@@ -2303,8 +2303,8 @@
       <c r="P36" t="str">
         <v>UPG-300-3013-S1</v>
       </c>
-      <c r="Q36">
-        <v>1</v>
+      <c r="Q36" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="37">
@@ -2356,8 +2356,8 @@
       <c r="P37" t="str">
         <v>UPG-300-3014-S1</v>
       </c>
-      <c r="Q37">
-        <v>1</v>
+      <c r="Q37" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="38">
@@ -2409,8 +2409,8 @@
       <c r="P38" t="str">
         <v>UPG-300-3015-S1</v>
       </c>
-      <c r="Q38">
-        <v>1</v>
+      <c r="Q38" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="39">
@@ -2462,8 +2462,8 @@
       <c r="P39" t="str">
         <v>UPG-300-3016-S1</v>
       </c>
-      <c r="Q39">
-        <v>1</v>
+      <c r="Q39" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="40">
@@ -2515,8 +2515,8 @@
       <c r="P40" t="str">
         <v>UPG-300-3017-S1</v>
       </c>
-      <c r="Q40">
-        <v>1</v>
+      <c r="Q40" t="str">
+        <v>R0</v>
       </c>
     </row>
     <row r="41">
@@ -2568,8 +2568,8 @@
       <c r="P41" t="str">
         <v>UPG-300-3018-S1</v>
       </c>
-      <c r="Q41">
-        <v>1</v>
+      <c r="Q41" t="str">
+        <v>R0</v>
       </c>
     </row>
   </sheetData>
